--- a/filesystem/Finance/Billing/FenwickGenomics_Oct2025_statement.xlsx
+++ b/filesystem/Finance/Billing/FenwickGenomics_Oct2025_statement.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -183,6 +183,17 @@
       <color rgb="002563EB"/>
       <sz val="9.5"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="12">
@@ -250,7 +261,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -562,11 +573,222 @@
         <color rgb="00BBF7D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="medium">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBF7D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBF7D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBF7D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBF7D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00166534"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBF7D0"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00166534"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -744,6 +966,52 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,13 +1340,6 @@
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="19" t="n"/>
-      <c r="D1" s="19" t="n"/>
-      <c r="E1" s="19" t="n"/>
-      <c r="F1" s="19" t="n"/>
-      <c r="G1" s="19" t="n"/>
-      <c r="H1" s="19" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
@@ -1086,56 +1347,35 @@
           <t>Monthly Billing Statement</t>
         </is>
       </c>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>227 Alexander Drive, Suite 400  •  Durham, NC 27709</t>
         </is>
       </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="n"/>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="21" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>EIN: 47-3812905  •  Phone: +1 (919) 555-0142  •  billing@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5" ht="14" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="64" t="inlineStr">
         <is>
           <t>STATEMENT</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="B6" s="65" t="n"/>
+      <c r="C6" s="65" t="n"/>
+      <c r="D6" s="65" t="n"/>
+      <c r="E6" s="65" t="n"/>
+      <c r="F6" s="65" t="n"/>
+      <c r="G6" s="65" t="n"/>
+      <c r="H6" s="66" t="n"/>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
@@ -1143,17 +1383,17 @@
           <t>Statement Number</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="67" t="inlineStr">
         <is>
           <t>STMT-2025-10-0198</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="28" t="n"/>
+      <c r="C7" s="68" t="n"/>
+      <c r="D7" s="68" t="n"/>
+      <c r="E7" s="68" t="n"/>
+      <c r="F7" s="68" t="n"/>
+      <c r="G7" s="68" t="n"/>
+      <c r="H7" s="69" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
@@ -1161,17 +1401,17 @@
           <t>Statement Date</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="67" t="inlineStr">
         <is>
           <t>10/01/2025</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="28" t="n"/>
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="68" t="n"/>
+      <c r="E8" s="68" t="n"/>
+      <c r="F8" s="68" t="n"/>
+      <c r="G8" s="68" t="n"/>
+      <c r="H8" s="69" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -1179,17 +1419,17 @@
           <t>Statement Period</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="67" t="inlineStr">
         <is>
           <t>10/01/2025 – 10/31/2025</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="28" t="n"/>
+      <c r="C9" s="68" t="n"/>
+      <c r="D9" s="68" t="n"/>
+      <c r="E9" s="68" t="n"/>
+      <c r="F9" s="68" t="n"/>
+      <c r="G9" s="68" t="n"/>
+      <c r="H9" s="69" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
@@ -1197,17 +1437,17 @@
           <t>Billing Cycle</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="67" t="inlineStr">
         <is>
           <t>October 2025</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="28" t="n"/>
+      <c r="C10" s="68" t="n"/>
+      <c r="D10" s="68" t="n"/>
+      <c r="E10" s="68" t="n"/>
+      <c r="F10" s="68" t="n"/>
+      <c r="G10" s="68" t="n"/>
+      <c r="H10" s="69" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -1215,17 +1455,17 @@
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="67" t="inlineStr">
         <is>
           <t>Net 30</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="28" t="n"/>
+      <c r="C11" s="68" t="n"/>
+      <c r="D11" s="68" t="n"/>
+      <c r="E11" s="68" t="n"/>
+      <c r="F11" s="68" t="n"/>
+      <c r="G11" s="68" t="n"/>
+      <c r="H11" s="69" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
@@ -1233,32 +1473,32 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="28" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="68" t="n"/>
+      <c r="E12" s="68" t="n"/>
+      <c r="F12" s="68" t="n"/>
+      <c r="G12" s="68" t="n"/>
+      <c r="H12" s="69" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+      <c r="A14" s="64" t="inlineStr">
         <is>
           <t>BILL TO</t>
         </is>
       </c>
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="23" t="n"/>
-      <c r="H14" s="24" t="n"/>
+      <c r="B14" s="65" t="n"/>
+      <c r="C14" s="65" t="n"/>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="65" t="n"/>
+      <c r="H14" s="66" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
@@ -1266,17 +1506,17 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="67" t="inlineStr">
         <is>
           <t>Fenwick Genomics, Inc.</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="28" t="n"/>
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="68" t="n"/>
+      <c r="E15" s="68" t="n"/>
+      <c r="F15" s="68" t="n"/>
+      <c r="G15" s="68" t="n"/>
+      <c r="H15" s="69" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
@@ -1284,17 +1524,17 @@
           <t>Address</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="67" t="inlineStr">
         <is>
           <t>Waltham, MA</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="28" t="n"/>
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="68" t="n"/>
+      <c r="E16" s="68" t="n"/>
+      <c r="F16" s="68" t="n"/>
+      <c r="G16" s="68" t="n"/>
+      <c r="H16" s="69" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -1302,17 +1542,17 @@
           <t>ERPNext Customer ID</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="67" t="inlineStr">
         <is>
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="28" t="n"/>
+      <c r="C17" s="68" t="n"/>
+      <c r="D17" s="68" t="n"/>
+      <c r="E17" s="68" t="n"/>
+      <c r="F17" s="68" t="n"/>
+      <c r="G17" s="68" t="n"/>
+      <c r="H17" s="69" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
@@ -1320,17 +1560,17 @@
           <t>Account Origin</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="67" t="inlineStr">
         <is>
           <t>Inherited — Bramwell</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="28" t="n"/>
+      <c r="C18" s="68" t="n"/>
+      <c r="D18" s="68" t="n"/>
+      <c r="E18" s="68" t="n"/>
+      <c r="F18" s="68" t="n"/>
+      <c r="G18" s="68" t="n"/>
+      <c r="H18" s="69" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
@@ -1338,17 +1578,17 @@
           <t>Sales Order of Record</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="67" t="inlineStr">
         <is>
           <t>SO-2025-0417</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="28" t="n"/>
+      <c r="C19" s="68" t="n"/>
+      <c r="D19" s="68" t="n"/>
+      <c r="E19" s="68" t="n"/>
+      <c r="F19" s="68" t="n"/>
+      <c r="G19" s="68" t="n"/>
+      <c r="H19" s="69" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
@@ -1356,32 +1596,32 @@
           <t>MSA Term</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="67" t="inlineStr">
         <is>
           <t>04/01/2025 – 03/31/2026</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="28" t="n"/>
+      <c r="C20" s="68" t="n"/>
+      <c r="D20" s="68" t="n"/>
+      <c r="E20" s="68" t="n"/>
+      <c r="F20" s="68" t="n"/>
+      <c r="G20" s="68" t="n"/>
+      <c r="H20" s="69" t="n"/>
     </row>
     <row r="21" ht="14" customHeight="1"/>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="64" t="inlineStr">
         <is>
           <t>LINE ITEMS</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="24" t="n"/>
+      <c r="B22" s="65" t="n"/>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="66" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="29" t="inlineStr">
@@ -1491,10 +1731,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F25" s="38" t="n">
+      <c r="F25" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1531,10 +1771,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="39" t="inlineStr">
+      <c r="G26" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1571,10 +1811,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F27" s="38" t="n">
+      <c r="F27" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1611,10 +1851,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F28" s="40" t="n">
+      <c r="F28" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="39" t="inlineStr">
+      <c r="G28" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1651,10 +1891,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F29" s="38" t="n">
+      <c r="F29" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="39" t="inlineStr">
+      <c r="G29" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1691,10 +1931,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="72" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="39" t="inlineStr">
+      <c r="G30" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1731,10 +1971,10 @@
           <t>10/31/2025</t>
         </is>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F31" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="39" t="inlineStr">
+      <c r="G31" s="71" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1747,18 +1987,18 @@
     </row>
     <row r="32" ht="14" customHeight="1"/>
     <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="64" t="inlineStr">
         <is>
           <t>STATEMENT TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="23" t="n"/>
-      <c r="H33" s="24" t="n"/>
+      <c r="B33" s="65" t="n"/>
+      <c r="C33" s="65" t="n"/>
+      <c r="D33" s="65" t="n"/>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="65" t="n"/>
+      <c r="G33" s="65" t="n"/>
+      <c r="H33" s="66" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="41" t="inlineStr">
@@ -1766,15 +2006,15 @@
           <t>Subtotal — Retainer</t>
         </is>
       </c>
-      <c r="B34" s="42" t="n">
+      <c r="B34" s="73" t="n">
         <v>8500</v>
       </c>
-      <c r="C34" s="43" t="n"/>
-      <c r="D34" s="43" t="n"/>
-      <c r="E34" s="43" t="n"/>
-      <c r="F34" s="43" t="n"/>
-      <c r="G34" s="43" t="n"/>
-      <c r="H34" s="44" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="68" t="n"/>
+      <c r="H34" s="69" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="41" t="inlineStr">
@@ -1782,15 +2022,15 @@
           <t>Subtotal — Reimbursables</t>
         </is>
       </c>
-      <c r="B35" s="42" t="n">
+      <c r="B35" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="43" t="n"/>
-      <c r="E35" s="43" t="n"/>
-      <c r="F35" s="43" t="n"/>
-      <c r="G35" s="43" t="n"/>
-      <c r="H35" s="44" t="n"/>
+      <c r="C35" s="68" t="n"/>
+      <c r="D35" s="68" t="n"/>
+      <c r="E35" s="68" t="n"/>
+      <c r="F35" s="68" t="n"/>
+      <c r="G35" s="68" t="n"/>
+      <c r="H35" s="69" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="41" t="inlineStr">
@@ -1798,15 +2038,15 @@
           <t>Adjustments</t>
         </is>
       </c>
-      <c r="B36" s="42" t="n">
+      <c r="B36" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="43" t="n"/>
-      <c r="D36" s="43" t="n"/>
-      <c r="E36" s="43" t="n"/>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="43" t="n"/>
-      <c r="H36" s="44" t="n"/>
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="68" t="n"/>
+      <c r="H36" s="69" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="45" t="inlineStr">
@@ -1814,15 +2054,15 @@
           <t>Total Due for October 2025</t>
         </is>
       </c>
-      <c r="B37" s="46" t="n">
+      <c r="B37" s="74" t="n">
         <v>8500</v>
       </c>
-      <c r="C37" s="47" t="n"/>
-      <c r="D37" s="47" t="n"/>
-      <c r="E37" s="47" t="n"/>
-      <c r="F37" s="47" t="n"/>
-      <c r="G37" s="47" t="n"/>
-      <c r="H37" s="48" t="n"/>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="75" t="n"/>
+      <c r="E37" s="75" t="n"/>
+      <c r="F37" s="75" t="n"/>
+      <c r="G37" s="75" t="n"/>
+      <c r="H37" s="76" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="41" t="inlineStr">
@@ -1830,15 +2070,15 @@
           <t>Payments Received</t>
         </is>
       </c>
-      <c r="B38" s="49" t="n">
+      <c r="B38" s="77" t="n">
         <v>-8500</v>
       </c>
-      <c r="C38" s="50" t="n"/>
-      <c r="D38" s="50" t="n"/>
-      <c r="E38" s="50" t="n"/>
-      <c r="F38" s="50" t="n"/>
-      <c r="G38" s="50" t="n"/>
-      <c r="H38" s="51" t="n"/>
+      <c r="C38" s="68" t="n"/>
+      <c r="D38" s="68" t="n"/>
+      <c r="E38" s="68" t="n"/>
+      <c r="F38" s="68" t="n"/>
+      <c r="G38" s="68" t="n"/>
+      <c r="H38" s="69" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="52" t="inlineStr">
@@ -1846,45 +2086,45 @@
           <t>Balance</t>
         </is>
       </c>
-      <c r="B39" s="53" t="n">
+      <c r="B39" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="54" t="n"/>
-      <c r="D39" s="54" t="n"/>
-      <c r="E39" s="54" t="n"/>
-      <c r="F39" s="54" t="n"/>
-      <c r="G39" s="54" t="n"/>
-      <c r="H39" s="55" t="n"/>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+      <c r="F39" s="79" t="n"/>
+      <c r="G39" s="79" t="n"/>
+      <c r="H39" s="80" t="n"/>
     </row>
     <row r="40" ht="10" customHeight="1"/>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="81" t="inlineStr">
         <is>
           <t>Remittance confirmed via ACH on 10/01/2025. No balance carried into November cycle.</t>
         </is>
       </c>
-      <c r="B41" s="57" t="n"/>
-      <c r="C41" s="57" t="n"/>
-      <c r="D41" s="57" t="n"/>
-      <c r="E41" s="57" t="n"/>
-      <c r="F41" s="57" t="n"/>
-      <c r="G41" s="57" t="n"/>
-      <c r="H41" s="58" t="n"/>
+      <c r="B41" s="82" t="n"/>
+      <c r="C41" s="82" t="n"/>
+      <c r="D41" s="82" t="n"/>
+      <c r="E41" s="82" t="n"/>
+      <c r="F41" s="82" t="n"/>
+      <c r="G41" s="82" t="n"/>
+      <c r="H41" s="83" t="n"/>
     </row>
     <row r="42" ht="14" customHeight="1"/>
     <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="A43" s="64" t="inlineStr">
         <is>
           <t>REMITTANCE &amp; REFERENCE</t>
         </is>
       </c>
-      <c r="B43" s="23" t="n"/>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="23" t="n"/>
-      <c r="F43" s="23" t="n"/>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="24" t="n"/>
+      <c r="B43" s="65" t="n"/>
+      <c r="C43" s="65" t="n"/>
+      <c r="D43" s="65" t="n"/>
+      <c r="E43" s="65" t="n"/>
+      <c r="F43" s="65" t="n"/>
+      <c r="G43" s="65" t="n"/>
+      <c r="H43" s="66" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
@@ -1892,17 +2132,17 @@
           <t>Remit To</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="B44" s="67" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc., Attn: Accounts Receivable, 227 Alexander Drive, Suite 400, Durham, NC 27709</t>
         </is>
       </c>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
-      <c r="H44" s="28" t="n"/>
+      <c r="C44" s="68" t="n"/>
+      <c r="D44" s="68" t="n"/>
+      <c r="E44" s="68" t="n"/>
+      <c r="F44" s="68" t="n"/>
+      <c r="G44" s="68" t="n"/>
+      <c r="H44" s="69" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
@@ -1910,17 +2150,17 @@
           <t>ERPNext Sales Order</t>
         </is>
       </c>
-      <c r="B45" s="26" t="inlineStr">
+      <c r="B45" s="67" t="inlineStr">
         <is>
           <t>SO-2025-0417</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="28" t="n"/>
+      <c r="C45" s="68" t="n"/>
+      <c r="D45" s="68" t="n"/>
+      <c r="E45" s="68" t="n"/>
+      <c r="F45" s="68" t="n"/>
+      <c r="G45" s="68" t="n"/>
+      <c r="H45" s="69" t="n"/>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
@@ -1928,17 +2168,17 @@
           <t>ERPNext Customer ID</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="67" t="inlineStr">
         <is>
           <t>CUST-2025-0198</t>
         </is>
       </c>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="27" t="n"/>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
-      <c r="H46" s="28" t="n"/>
+      <c r="C46" s="68" t="n"/>
+      <c r="D46" s="68" t="n"/>
+      <c r="E46" s="68" t="n"/>
+      <c r="F46" s="68" t="n"/>
+      <c r="G46" s="68" t="n"/>
+      <c r="H46" s="69" t="n"/>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
@@ -1946,32 +2186,25 @@
           <t>Invoice Questions</t>
         </is>
       </c>
-      <c r="B47" s="26" t="inlineStr">
+      <c r="B47" s="67" t="inlineStr">
         <is>
           <t>alan.rutherford@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
-      <c r="H47" s="28" t="n"/>
+      <c r="C47" s="68" t="n"/>
+      <c r="D47" s="68" t="n"/>
+      <c r="E47" s="68" t="n"/>
+      <c r="F47" s="68" t="n"/>
+      <c r="G47" s="68" t="n"/>
+      <c r="H47" s="69" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1"/>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="59" t="inlineStr">
+      <c r="A49" s="84" t="inlineStr">
         <is>
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B49" s="59" t="n"/>
-      <c r="C49" s="59" t="n"/>
-      <c r="D49" s="59" t="n"/>
-      <c r="E49" s="59" t="n"/>
-      <c r="F49" s="59" t="n"/>
-      <c r="G49" s="59" t="n"/>
-      <c r="H49" s="59" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="60" t="inlineStr">
@@ -1979,13 +2212,6 @@
           <t>Alan Rutherford</t>
         </is>
       </c>
-      <c r="B50" s="60" t="n"/>
-      <c r="C50" s="60" t="n"/>
-      <c r="D50" s="60" t="n"/>
-      <c r="E50" s="60" t="n"/>
-      <c r="F50" s="60" t="n"/>
-      <c r="G50" s="60" t="n"/>
-      <c r="H50" s="60" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="61" t="inlineStr">
@@ -1993,27 +2219,13 @@
           <t>Finance Director</t>
         </is>
       </c>
-      <c r="B51" s="61" t="n"/>
-      <c r="C51" s="61" t="n"/>
-      <c r="D51" s="61" t="n"/>
-      <c r="E51" s="61" t="n"/>
-      <c r="F51" s="61" t="n"/>
-      <c r="G51" s="61" t="n"/>
-      <c r="H51" s="61" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="63" t="inlineStr">
         <is>
           <t>Thornfield Life Sciences Marketing, Inc.</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="62" t="inlineStr">
@@ -2021,13 +2233,6 @@
           <t>alan.rutherford@thornfieldlsm.com</t>
         </is>
       </c>
-      <c r="B53" s="62" t="n"/>
-      <c r="C53" s="62" t="n"/>
-      <c r="D53" s="62" t="n"/>
-      <c r="E53" s="62" t="n"/>
-      <c r="F53" s="62" t="n"/>
-      <c r="G53" s="62" t="n"/>
-      <c r="H53" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">
